--- a/human_resources_forms/023_entry_level_accountant_interview_form--human_resources_forms.xlsx
+++ b/human_resources_forms/023_entry_level_accountant_interview_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'0-2_years'}</t>
+          <t>0-2_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '0-2 years'}</t>
+          <t>0-2 years</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'microsoft_office'}</t>
+          <t>microsoft_office</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Microsoft Office'}</t>
+          <t>Microsoft Office</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'google_suite'}</t>
+          <t>google_suite</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Google Suite'}</t>
+          <t>Google Suite</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'quickbooks'}</t>
+          <t>quickbooks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'QuickBooks'}</t>
+          <t>QuickBooks</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
